--- a/player_scores.xlsx
+++ b/player_scores.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.02414554235419717</v>
+        <v>-0.02414554235419716</v>
       </c>
     </row>
     <row r="3">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.05399691724685716</v>
+        <v>-0.05399691724685714</v>
       </c>
     </row>
     <row r="7">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.04538936948287684</v>
+        <v>-0.04538936948287682</v>
       </c>
     </row>
     <row r="9">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05595878353972511</v>
+        <v>0.05595878353972512</v>
       </c>
     </row>
     <row r="16">
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.05593422247865686</v>
+        <v>-0.05593422247865688</v>
       </c>
     </row>
     <row r="20">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.2131216748485474</v>
+        <v>-0.2131216748485473</v>
       </c>
     </row>
     <row r="24">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.01482329673449276</v>
+        <v>-0.01482329673449275</v>
       </c>
     </row>
     <row r="27">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.09745808580017103</v>
+        <v>0.09745808580017104</v>
       </c>
     </row>
     <row r="29">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.08536670433118942</v>
+        <v>0.08536670433118944</v>
       </c>
     </row>
     <row r="33">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.008424866312576402</v>
+        <v>-0.008424866312576411</v>
       </c>
     </row>
     <row r="35">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.08639293143202467</v>
+        <v>-0.08639293143202466</v>
       </c>
     </row>
     <row r="39">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.002213946133020311</v>
+        <v>0.0022139461330203</v>
       </c>
     </row>
     <row r="45">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.08317388556535235</v>
+        <v>0.08317388556535238</v>
       </c>
     </row>
     <row r="46">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.05397937150666648</v>
+        <v>0.05397937150666649</v>
       </c>
     </row>
     <row r="47">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-0.02198896130691561</v>
+        <v>-0.02198896130691562</v>
       </c>
     </row>
     <row r="48">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.04668965534701248</v>
+        <v>0.0466896553470125</v>
       </c>
     </row>
     <row r="49">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.08393785082728504</v>
+        <v>0.08393785082728503</v>
       </c>
     </row>
     <row r="51">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.03105087175878767</v>
+        <v>-0.03105087175878766</v>
       </c>
     </row>
     <row r="53">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.01129998826531301</v>
+        <v>-0.01129998826531299</v>
       </c>
     </row>
     <row r="62">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0006186982537491959</v>
+        <v>-0.0006186982537491841</v>
       </c>
     </row>
     <row r="63">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.03629156657143762</v>
+        <v>0.03629156657143761</v>
       </c>
     </row>
     <row r="64">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.04077676658154627</v>
+        <v>-0.04077676658154625</v>
       </c>
     </row>
     <row r="65">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.03303857409723558</v>
+        <v>0.0330385740972356</v>
       </c>
     </row>
     <row r="67">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.006316763474615402</v>
+        <v>0.006316763474615425</v>
       </c>
     </row>
     <row r="68">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.04426801070943757</v>
+        <v>-0.04426801070943756</v>
       </c>
     </row>
     <row r="69">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.02667979303651471</v>
+        <v>-0.0266797930365147</v>
       </c>
     </row>
     <row r="71">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.007770692900223957</v>
+        <v>0.007770692900223961</v>
       </c>
     </row>
     <row r="73">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.1413638925215453</v>
+        <v>-0.1413638925215452</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.0005749438942764044</v>
+        <v>0.0005749438942764089</v>
       </c>
     </row>
     <row r="77">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.09047568794228567</v>
+        <v>0.09047568794228569</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.0001327545071111812</v>
+        <v>0.0001327545071111856</v>
       </c>
     </row>
     <row r="80">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-0.06913289682770833</v>
+        <v>-0.06913289682770832</v>
       </c>
     </row>
     <row r="86">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-0.02071661391197662</v>
+        <v>-0.0207166139119766</v>
       </c>
     </row>
     <row r="87">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>-0.01747482828950684</v>
+        <v>-0.01747482828950685</v>
       </c>
     </row>
     <row r="88">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.03733730773668794</v>
+        <v>0.03733730773668795</v>
       </c>
     </row>
     <row r="89">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.07604889764776318</v>
+        <v>0.07604889764776319</v>
       </c>
     </row>
     <row r="90">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.007215225529062209</v>
+        <v>0.007215225529062231</v>
       </c>
     </row>
     <row r="91">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.08323251993336171</v>
+        <v>0.08323251993336174</v>
       </c>
     </row>
     <row r="92">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-0.03781711460614754</v>
+        <v>-0.03781711460614756</v>
       </c>
     </row>
     <row r="93">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.04035679166499254</v>
+        <v>0.04035679166499256</v>
       </c>
     </row>
     <row r="94">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>-0.02659203785693141</v>
+        <v>-0.02659203785693139</v>
       </c>
     </row>
     <row r="97">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.08621751408550679</v>
+        <v>0.08621751408550681</v>
       </c>
     </row>
     <row r="99">
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-0.07733068319537707</v>
+        <v>-0.07733068319537709</v>
       </c>
     </row>
     <row r="102">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.02124978314754177</v>
+        <v>0.02124978314754178</v>
       </c>
     </row>
     <row r="103">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.01182268172289343</v>
+        <v>0.01182268172289342</v>
       </c>
     </row>
     <row r="104">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.04633479165276767</v>
+        <v>0.04633479165276766</v>
       </c>
     </row>
     <row r="105">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.00019035978284274</v>
+        <v>0.0001903597828427593</v>
       </c>
     </row>
     <row r="106">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-0.02629969870178938</v>
+        <v>-0.0262996987017894</v>
       </c>
     </row>
     <row r="109">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.001221039914576234</v>
+        <v>0.001221039914576241</v>
       </c>
     </row>
     <row r="110">
@@ -1527,7 +1527,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.04007678083919049</v>
+        <v>0.04007678083919051</v>
       </c>
     </row>
     <row r="111">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.01278087895008525</v>
+        <v>0.01278087895008524</v>
       </c>
     </row>
     <row r="114">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.02944911573110681</v>
+        <v>0.0294491157311068</v>
       </c>
     </row>
     <row r="115">
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-0.03742168493398917</v>
+        <v>-0.03742168493398918</v>
       </c>
     </row>
     <row r="116">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.05650414907813311</v>
+        <v>0.05650414907813312</v>
       </c>
     </row>
     <row r="117">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.1048061593561087</v>
+        <v>0.1048061593561086</v>
       </c>
     </row>
     <row r="118">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.0381814440516747</v>
+        <v>0.03818144405167471</v>
       </c>
     </row>
     <row r="119">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.1025257983012688</v>
+        <v>0.1025257983012687</v>
       </c>
     </row>
     <row r="120">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.09497933876085</v>
+        <v>0.09497933876084999</v>
       </c>
     </row>
     <row r="126">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.06380623037312762</v>
+        <v>0.0638062303731276</v>
       </c>
     </row>
     <row r="127">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>-0.02517308901803006</v>
+        <v>-0.02517308901803005</v>
       </c>
     </row>
     <row r="128">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.0193548015001186</v>
+        <v>0.01935480150011861</v>
       </c>
     </row>
     <row r="130">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>-0.07357463886133554</v>
+        <v>-0.07357463886133557</v>
       </c>
     </row>
     <row r="131">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0.05341572825929351</v>
+        <v>-0.0534157282592935</v>
       </c>
     </row>
     <row r="134">
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.0485883471230943</v>
+        <v>0.04858834712309429</v>
       </c>
     </row>
     <row r="136">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.02260439997202628</v>
+        <v>0.02260439997202629</v>
       </c>
     </row>
     <row r="139">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>-0.05195609420397863</v>
+        <v>-0.05195609420397864</v>
       </c>
     </row>
     <row r="140">
